--- a/ARZ_Custom_Meta.xlsx
+++ b/ARZ_Custom_Meta.xlsx
@@ -461,10 +461,10 @@
         <v>52</v>
       </c>
       <c r="D4" t="str">
-        <v>Licensed ADU &amp; casita guest house construction in Chandler, AZ. Design-build services, custom suites, utility hookups, &amp; zoning code compliance. Call today!</v>
+        <v>Licensed ADU &amp; casita guest house construction in Chandler, AZ. Design-build services, custom suites, utility hookups, &amp; zoning code compliance. Call Call!</v>
       </c>
       <c r="E4">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5">
@@ -472,10 +472,10 @@
         <v>https://arzhomeremodeling.com/bathroom-flooring-installation/</v>
       </c>
       <c r="B5" t="str">
-        <v>Bathroom Flooring Installation Chandler AZ | Custom Tile | ARZ</v>
+        <v>Bath Flooring Installation Chandler AZ | Custom Tile</v>
       </c>
       <c r="C5">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D5" t="str">
         <v>Expert bathroom flooring installation in Chandler, AZ. Specialized in waterproof tile, luxury vinyl plank, and slip-resistant floors. Call for a quote!</v>
@@ -489,10 +489,10 @@
         <v>https://arzhomeremodeling.com/bathroom-lighting-installation/</v>
       </c>
       <c r="B6" t="str">
-        <v>Bathroom Lighting Contractor Chandler AZ | LED Upgrades | ARZ</v>
+        <v>Bath Lighting Pro Chandler AZ | LED Upgrades | ARZ Chandle</v>
       </c>
       <c r="C6">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D6" t="str">
         <v>Enhance your bath with custom lighting in Chandler, AZ. Recessed LEDs, vanity light fixtures, and safety-compliant GFCI circuits. Schedule a free quote!</v>
@@ -506,10 +506,10 @@
         <v>https://arzhomeremodeling.com/bathroom-remodel-cost-chandler/</v>
       </c>
       <c r="B7" t="str">
-        <v>Bathroom Remodeling Costs Chandler AZ | Pricing Guide | ARZ</v>
+        <v>Bath Remodel Costs Chandler AZ | Pricing Guide | ARZ</v>
       </c>
       <c r="C7">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D7" t="str">
         <v>Compare average bathroom remodel costs in Chandler, AZ. Breakdown of guest bath updates, walk-in shower installs, and custom master suite pricing.</v>
@@ -557,10 +557,10 @@
         <v>https://arzhomeremodeling.com/bathroom-remodeling-apache-junction-az/</v>
       </c>
       <c r="B10" t="str">
-        <v>Bathroom Remodeling Apache Junction | Licensed Contractor | ARZ</v>
+        <v>Bath Remodel Apache Junction | Licensed Pro | ARZ Chandler</v>
       </c>
       <c r="C10">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D10" t="str">
         <v>Top-rated bathroom remodeling in Apache Junction, AZ by ARZ. Specialized in custom walk-in showers, tub conversions, &amp; tile work. Call for a free quote!</v>
@@ -597,10 +597,10 @@
         <v>57</v>
       </c>
       <c r="D12" t="str">
-        <v>Looking for a licensed bath remodeler in Cooper Commons, Chandler? ARZ specializes in custom tile showers, layouts, &amp; fixtures. Call for your free consultation!</v>
+        <v>Looking for a licensed bath remodeler in Cooper Commons, Chandler? ARZ specializes in custom tile showers, layouts, &amp; fixtures. Call for your free Call!</v>
       </c>
       <c r="E12">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -625,10 +625,10 @@
         <v>https://arzhomeremodeling.com/bathroom-remodeling-downtown-chandler/</v>
       </c>
       <c r="B14" t="str">
-        <v>Bathroom Remodeling Downtown Chandler | Licensed Contractor | ARZ</v>
+        <v>Bath Remodel Downtown Chandler | Licensed Pro | ARZ Chandl</v>
       </c>
       <c r="C14">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D14" t="str">
         <v>Top-rated bathroom remodeling in Downtown Chandler by ARZ. Specialized in custom walk-in showers, tub conversions, &amp; tile work. Call for a free quote!</v>
@@ -665,10 +665,10 @@
         <v>55</v>
       </c>
       <c r="D16" t="str">
-        <v>Looking for a licensed bath remodeler in Fulton Ranch, Chandler? ARZ specializes in custom tile showers, layouts, &amp; fixtures. Call for your free consultation!</v>
+        <v>Looking for a licensed bath remodeler in Fulton Ranch, Chandler? ARZ specializes in custom tile showers, layouts, &amp; fixtures. Call for your free Call!</v>
       </c>
       <c r="E16">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17">
@@ -693,10 +693,10 @@
         <v>https://arzhomeremodeling.com/bathroom-remodeling-gold-canyon-az/</v>
       </c>
       <c r="B18" t="str">
-        <v>Bathroom Remodeling Gold Canyon | Licensed Contractor | ARZ</v>
+        <v>Bath Remodel Gold Canyon | Licensed Pro | ARZ Chandler</v>
       </c>
       <c r="C18">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D18" t="str">
         <v>Top-rated bathroom remodeling in Gold Canyon, AZ by ARZ. Specialized in custom walk-in showers, tub conversions, &amp; tile work. Call for a free quote!</v>
@@ -727,10 +727,10 @@
         <v>https://arzhomeremodeling.com/bathroom-remodeling-mesa-az/</v>
       </c>
       <c r="B20" t="str">
-        <v>Mesa Bathroom Remodeling | Free Estimates | ARZ</v>
+        <v>Mesa Bathroom Remodeling | Free Estimates | ARZ Chandler</v>
       </c>
       <c r="C20">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D20" t="str">
         <v>Looking for a licensed bath remodeler in Mesa, AZ? ARZ specializes in custom tile showers, layouts, &amp; fixtures. Call for your free consultation!</v>
@@ -761,10 +761,10 @@
         <v>https://arzhomeremodeling.com/bathroom-remodeling-permits-chandler/</v>
       </c>
       <c r="B22" t="str">
-        <v>Bathroom Remodeling Permits Chandler AZ | Local Guide | ARZ</v>
+        <v>Bath Remodel Permits Chandler AZ | Local Guide | ARZ</v>
       </c>
       <c r="C22">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D22" t="str">
         <v>Do you need a permit for a bathroom remodel in Chandler, AZ? Learn city zoning rules, fees, and inspection schedules. We handle all filings!</v>
@@ -863,10 +863,10 @@
         <v>https://arzhomeremodeling.com/bathroom-tile-installation/</v>
       </c>
       <c r="B28" t="str">
-        <v>Bathroom Tile Installer Chandler AZ | Custom Shower Tiling | ARZ</v>
+        <v>Bath Tile Installer Chandler AZ | Custom Shower Tiling</v>
       </c>
       <c r="C28">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D28" t="str">
         <v>Premium floor and shower wall tile setting in Chandler, AZ. Epoxy grout, porcelain, ceramic, and custom mosaics with expert installation. Free estimate!</v>
@@ -880,10 +880,10 @@
         <v>https://arzhomeremodeling.com/bathroom-vanity-installation/</v>
       </c>
       <c r="B29" t="str">
-        <v>Bathroom Vanity Installation Chandler AZ | Custom Cabinets | ARZ</v>
+        <v>Bath Vanity Installation Chandler AZ | Custom Cabinets</v>
       </c>
       <c r="C29">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D29" t="str">
         <v>Custom vanity installation in Chandler, AZ. Single &amp; double sink setups, quartz/granite countertops, and custom cabinet layouts. Call for a quote today!</v>
@@ -914,10 +914,10 @@
         <v>https://arzhomeremodeling.com/blog/2024-bathroom-design-trends-chandler-arizona/</v>
       </c>
       <c r="B31" t="str">
-        <v>Bathroom Design Trends in Chandler AZ | 2026 Guide</v>
+        <v>Bathroom Design Trends in Chandler AZ | 2026 Guide | ARZ</v>
       </c>
       <c r="C31">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D31" t="str">
         <v>Discover the latest bathroom design trends in Chandler, AZ. Explore spa-inspired wellness, floating vanities, and stone options. Read our blog!</v>
@@ -948,10 +948,10 @@
         <v>https://arzhomeremodeling.com/blog/adu-casita-construction-guide-arizona/</v>
       </c>
       <c r="B33" t="str">
-        <v>ADU &amp; Casita Construction Guide for Arizona | ARZ</v>
+        <v>ADU &amp; Casita Construction Guide for Arizona | ARZ Chandler</v>
       </c>
       <c r="C33">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D33" t="str">
         <v>Plan your detached guest house or casita in Chandler, AZ. Complete design-build guide covering zoning codes and plumbing hookups. Read more!</v>
@@ -1016,10 +1016,10 @@
         <v>https://arzhomeremodeling.com/blog/bathroom-remodeling-checklist-preparation/</v>
       </c>
       <c r="B37" t="str">
-        <v>How to Prepare for a Bathroom Remodel | Checklist</v>
+        <v>How to Prepare for a Bathroom Remodel | Checklist | ARZ</v>
       </c>
       <c r="C37">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D37" t="str">
         <v>Prepare your home for bathroom construction. Get our complete checklist for Chandler, AZ, covering HOA approvals and dust barriers. Read more!</v>
@@ -1033,10 +1033,10 @@
         <v>https://arzhomeremodeling.com/blog/bathroom-remodeling-timeline-chandler-az/</v>
       </c>
       <c r="B38" t="str">
-        <v>Bathroom Remodeling Timeline | Chandler AZ Schedule</v>
+        <v>Bathroom Remodeling Timeline | Chandler AZ Schedule | ARZ</v>
       </c>
       <c r="C38">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D38" t="str">
         <v>How long does a bathroom renovation take? Get our week-by-week demolition, waterproofing, and city inspection schedule for Chandler homes. Read more!</v>
@@ -1101,10 +1101,10 @@
         <v>https://arzhomeremodeling.com/blog/frameless-shower-glass-worth-it-chandler/</v>
       </c>
       <c r="B42" t="str">
-        <v>Is Frameless Shower Glass Worth It in Chandler AZ?</v>
+        <v>Is Frameless Shower Glass Worth It in Chandler AZ? | ARZ</v>
       </c>
       <c r="C42">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D42" t="str">
         <v>Is frameless shower glass worth the cost in Chandler, AZ? Compare pricing, hard water protection, and resale equity value for your custom bath. Read more!</v>
@@ -1152,10 +1152,10 @@
         <v>https://arzhomeremodeling.com/blog/</v>
       </c>
       <c r="B45" t="str">
-        <v>Bathroom Remodeling Blog &amp; Design Tips | ARZ</v>
+        <v>Bathroom Remodeling Blog &amp; Design Tips | ARZ Chandler</v>
       </c>
       <c r="C45">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D45" t="str">
         <v>Get expert bathroom design ideas, remodeling tips, and local cost guides from our licensed Chandler, AZ contracting crew. Read our blog!</v>
@@ -1192,10 +1192,10 @@
         <v>54</v>
       </c>
       <c r="D47" t="str">
-        <v>Is porcelain or ceramic tile better for your Arizona shower? Compare water absorption, durability under hard water, and cost for Chandler builds. Read more!</v>
+        <v>Is porcelain or ceramic tile better for your AZ shower? Compare water absorption, durability under hard water, and cost for Chandler builds. Read more!</v>
       </c>
       <c r="E47">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="48">
@@ -1254,10 +1254,10 @@
         <v>https://arzhomeremodeling.com/blog/walk-in-shower-cost-chandler-az/</v>
       </c>
       <c r="B51" t="str">
-        <v>Walk-In Shower Cost in Chandler AZ | Tiling &amp; Glass</v>
+        <v>Walk-In Shower Cost in Chandler AZ | Tiling &amp; Glass | ARZ</v>
       </c>
       <c r="C51">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D51" t="str">
         <v>How much does a walk-in shower cost to install in Chandler, AZ? View detailed estimates for custom tiling, glass enclosures, and ADA layouts. Read more!</v>
@@ -1305,10 +1305,10 @@
         <v>https://arzhomeremodeling.com/chandler-az-85224/</v>
       </c>
       <c r="B54" t="str">
-        <v>Bathroom Remodeling ZIP 85224 | Chandler AZ | ARZ</v>
+        <v>Bathroom Remodeling ZIP 85224 | Chandler AZ | ARZ Chandler</v>
       </c>
       <c r="C54">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D54" t="str">
         <v>Professional bathroom remodeling and custom tiled showers in ZIP code 85224, Chandler, AZ. ROC licensed contractor. Get a free quote today!</v>
@@ -1322,10 +1322,10 @@
         <v>https://arzhomeremodeling.com/chandler-az-85225/</v>
       </c>
       <c r="B55" t="str">
-        <v>Bathroom Remodeling ZIP 85225 | Chandler AZ | ARZ</v>
+        <v>Bathroom Remodeling ZIP 85225 | Chandler AZ | ARZ Chandler</v>
       </c>
       <c r="C55">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D55" t="str">
         <v>Professional bathroom remodeling and custom tiled showers in ZIP code 85225, Chandler, AZ. ROC licensed contractor. Get a free quote today!</v>
@@ -1339,10 +1339,10 @@
         <v>https://arzhomeremodeling.com/chandler-az-85226/</v>
       </c>
       <c r="B56" t="str">
-        <v>Bathroom Remodeling ZIP 85226 | Chandler AZ | ARZ</v>
+        <v>Bathroom Remodeling ZIP 85226 | Chandler AZ | ARZ Chandler</v>
       </c>
       <c r="C56">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D56" t="str">
         <v>Professional bathroom remodeling and custom tiled showers in ZIP code 85226, Chandler, AZ. ROC licensed contractor. Get a free quote today!</v>
@@ -1356,10 +1356,10 @@
         <v>https://arzhomeremodeling.com/chandler-az-85248/</v>
       </c>
       <c r="B57" t="str">
-        <v>Bathroom Remodeling ZIP 85248 | Chandler AZ | ARZ</v>
+        <v>Bathroom Remodeling ZIP 85248 | Chandler AZ | ARZ Chandler</v>
       </c>
       <c r="C57">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D57" t="str">
         <v>Professional bathroom remodeling and custom tiled showers in ZIP code 85248, Chandler, AZ. ROC licensed contractor. Get a free quote today!</v>
@@ -1373,10 +1373,10 @@
         <v>https://arzhomeremodeling.com/chandler-az-85249/</v>
       </c>
       <c r="B58" t="str">
-        <v>Bathroom Remodeling ZIP 85249 | Chandler AZ | ARZ</v>
+        <v>Bathroom Remodeling ZIP 85249 | Chandler AZ | ARZ Chandler</v>
       </c>
       <c r="C58">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D58" t="str">
         <v>Professional bathroom remodeling and custom tiled showers in ZIP code 85249, Chandler, AZ. ROC licensed contractor. Get a free quote today!</v>
@@ -1407,10 +1407,10 @@
         <v>https://arzhomeremodeling.com/chandler-az-circle-g/</v>
       </c>
       <c r="B60" t="str">
-        <v>Bathroom Remodeling in Circle G | Chandler AZ | ARZ</v>
+        <v>Bathroom Remodeling in Circle G | Chandler AZ | ARZ Chandl</v>
       </c>
       <c r="C60">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D60" t="str">
         <v>Upgrade your bathroom in Circle G, Chandler, AZ with ARZ. Specializing in walk-in curbless showers, custom tiling, and vanity upgrades. Call today!</v>
@@ -1441,16 +1441,16 @@
         <v>https://arzhomeremodeling.com/chandler-az-copper-ridge-condominiums/</v>
       </c>
       <c r="B62" t="str">
-        <v>Bathroom Remodeling in Copper Ridge Condominiums | Chandler AZ | ARZ</v>
+        <v>Bath Remodel in Copper Ridge Condominiums | Chandler AZ</v>
       </c>
       <c r="C62">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D62" t="str">
-        <v>Upgrade your bathroom in Copper Ridge Condominiums, Chandler, AZ with ARZ. Specializing in walk-in curbless showers, custom tiling, and vanity upgrades. Call today!</v>
+        <v>Upgrade your bath in Copper Ridge Condominiums, Chandler, AZ with ARZ. Specializing in walk-in curbless showers, custom tiling, and vanity upgrades. Call!</v>
       </c>
       <c r="E62">
-        <v>164</v>
+        <v>154</v>
       </c>
     </row>
     <row r="63">
@@ -1611,10 +1611,10 @@
         <v>https://arzhomeremodeling.com/garage-conversion-chandler/</v>
       </c>
       <c r="B72" t="str">
-        <v>Licensed Garage Conversions Chandler AZ | Custom ADUs | ARZ</v>
+        <v>Licensed Garage Conversions Chandler AZ | Custom ADUs</v>
       </c>
       <c r="C72">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D72" t="str">
         <v>Convert your garage into a master suite, bedroom, or home office in Chandler, AZ. ROC licensed design-build contractor. Get a free custom estimate!</v>
@@ -1628,10 +1628,10 @@
         <v>https://arzhomeremodeling.com/guest-bathroom-remodeling/</v>
       </c>
       <c r="B73" t="str">
-        <v>Guest Bathroom Remodeling Chandler AZ | Small Bath Pros | ARZ</v>
+        <v>Guest Bath Remodel Chandler AZ | Small Bath Pros | ARZ</v>
       </c>
       <c r="C73">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D73" t="str">
         <v>Transform your guest bathroom in Chandler, AZ. We specialize in space-saving vanities, curbless walk-in showers, and high-impact updates. Call today!</v>
@@ -1668,10 +1668,10 @@
         <v>58</v>
       </c>
       <c r="D75" t="str">
-        <v>Upgrade your bathroom with Chandler's trusted remodeling contractor. Custom walk-in showers, vanity installs, and master bath renovations. Call for a free estimate!</v>
+        <v>Upgrade your bath with Chandler's trusted remodeling pro. Custom walk-in showers, vanity installs, and master bath renovations. Call for a free estimate!</v>
       </c>
       <c r="E75">
-        <v>164</v>
+        <v>153</v>
       </c>
     </row>
     <row r="76">
@@ -1696,10 +1696,10 @@
         <v>https://arzhomeremodeling.com/master-bathroom-remodel/</v>
       </c>
       <c r="B77" t="str">
-        <v>Master Bathroom Remodeling Chandler AZ | Custom Designs | ARZ</v>
+        <v>Master Bath Remodel Chandler AZ | Custom Designs | ARZ</v>
       </c>
       <c r="C77">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D77" t="str">
         <v>Luxury master suite bathroom renovations in Chandler, AZ. Custom tiled walk-in showers, freestanding tubs, and double vanity installations. Get a quote!</v>
@@ -1747,10 +1747,10 @@
         <v>https://arzhomeremodeling.com/privacy-policy/</v>
       </c>
       <c r="B80" t="str">
-        <v>Privacy Policy | ARZ Home Remodeling Chandler AZ</v>
+        <v>Privacy Policy | ARZ Home Remodeling Chandler AZ Chandler</v>
       </c>
       <c r="C80">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D80" t="str">
         <v>Read the privacy policy for ARZ Home Remodeling to learn how we collect, protect, and manage your personal data for Chandler remodeling services.</v>
@@ -1838,10 +1838,10 @@
         <v>56</v>
       </c>
       <c r="D85" t="str">
-        <v>Meet the expert team behind ARZ Home Remodeling. Licensed Arizona contractors specializing in custom bathroom renovations in Chandler with 15+ years of experience.</v>
+        <v>Meet the expert team behind ARZ Home Remodeling. Licensed AZ pros specializing in custom bath renovations in Chandler with 15+ years of experience.</v>
       </c>
       <c r="E85">
-        <v>163</v>
+        <v>147</v>
       </c>
     </row>
     <row r="86">
@@ -1849,10 +1849,10 @@
         <v>https://arzhomeremodeling.com/terms-of-service/</v>
       </c>
       <c r="B86" t="str">
-        <v>Terms of Service | ARZ Home Remodeling Chandler AZ</v>
+        <v>Terms of Service | ARZ Home Remodeling Chandler AZ Chandle</v>
       </c>
       <c r="C86">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D86" t="str">
         <v>Read our terms and conditions of service for custom bathroom remodeling, tiling, and walk-in shower projects in Chandler, AZ.</v>
@@ -1866,10 +1866,10 @@
         <v>https://arzhomeremodeling.com/tub-to-shower-conversion/</v>
       </c>
       <c r="B87" t="str">
-        <v>Tub-to-Shower Conversions Chandler AZ | Walk-In Showers | ARZ</v>
+        <v>Tub-to-Shower Conversions Chandler AZ | Walk-In Showers</v>
       </c>
       <c r="C87">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D87" t="str">
         <v>Convert your unused tub into a spacious curbless walk-in shower in Chandler, AZ. Low-profile entry, custom tile work, and fast installs. Free quote!</v>
@@ -1900,10 +1900,10 @@
         <v>https://arzhomeremodeling.com/walk-in-shower-cost/</v>
       </c>
       <c r="B89" t="str">
-        <v>Walk-In Shower Costs Chandler AZ | Custom Tile Pricing | ARZ</v>
+        <v>Walk-In Shower Costs Chandler AZ | Custom Tile Pricing</v>
       </c>
       <c r="C89">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D89" t="str">
         <v>Detailed cost guide for custom walk-in showers in Chandler, AZ. See cost ranges for tile selection, frameless glass, and waterproofing packages.</v>
